--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 142291억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+고객지수 4분기 이동합(t−3) 142294억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 149922억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+고객지수 4분기 이동합(t−3) 150036억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 156993억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+고객지수 4분기 이동합(t−3) 157217억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 151026억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+고객지수 4분기 이동합(t−3) 151360억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 150574억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+고객지수 4분기 이동합(t−3) 151017억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 149176억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+고객지수 4분기 이동합(t−3) 149619억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 146967억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+고객지수 4분기 이동합(t−3) 147411억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -924,25 +924,25 @@
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2737억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2738억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2898억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2899억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3154억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3156억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3385억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3388억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1815,43 +1815,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 142291억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−3) 142294억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 149922억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−3) 150036억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 156993억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−3) 157217억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 151026억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−3) 151360억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 150574억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−3) 151017억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 149176억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−3) 149619억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 146967억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−3) 147411억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2288,25 +2288,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2737억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2738억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2898억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2899억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3154억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3156억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3385억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3388억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6525,26 +6525,26 @@
         <v>0.008854000000000001</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.473991</v>
+        <v>0.474019</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.279546</v>
+        <v>0.280523</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.313291</v>
+        <v>0.31516</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.135313</v>
+        <v>0.137825</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.058214</v>
+        <v>0.061306</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.004975</v>
+        <v>-0.002783</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.06386699999999999</v>
+        <v>-0.062372</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6674,20 +6674,20 @@
         <v>0.07878499999999999</v>
       </c>
       <c r="AG22" s="24" t="n">
+        <v>0.07878300000000001</v>
+      </c>
+      <c r="AH22" s="24" t="n">
         <v>0.07878499999999999</v>
       </c>
-      <c r="AH22" s="24" t="n">
-        <v>0.078782</v>
-      </c>
       <c r="AI22" s="24" t="n">
-        <v>0.07878300000000001</v>
+        <v>0.07878400000000001</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.07878599999999999</v>
+        <v>0.078782</v>
       </c>
       <c r="AL22" s="24" t="n">
         <v>0.078782</v>
@@ -6829,23 +6829,23 @@
         <v>0.086462</v>
       </c>
       <c r="AG23" s="24" t="n">
+        <v>0.086463</v>
+      </c>
+      <c r="AH23" s="24" t="n">
+        <v>0.08645899999999999</v>
+      </c>
+      <c r="AI23" s="24" t="n">
         <v>0.086461</v>
-      </c>
-      <c r="AH23" s="24" t="n">
-        <v>0.086462</v>
-      </c>
-      <c r="AI23" s="24" t="n">
-        <v>0.086462</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.086463</v>
+        <v>0.086461</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.086461</v>
+        <v>0.086462</v>
       </c>
       <c r="AM23" s="24" t="n">
         <v>0.086461</v>
@@ -7122,10 +7122,10 @@
         <v>-17.17</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>-15.85</v>
+        <v>-15.84</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-14.66</v>
+        <v>-14.64</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7416,26 +7416,26 @@
         <v>0.049998</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.049981</v>
+        <v>0.049983</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.050006</v>
+        <v>0.049991</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.050009</v>
+        <v>0.050003</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.049987</v>
+        <v>0.050015</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.05001</v>
+        <v>0.050014</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.050002</v>
+        <v>0.049998</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7830,20 +7830,20 @@
         <v>0</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AH30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM30" s="29" t="n">
         <v>0</v>
@@ -7958,20 +7958,20 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
         <v>0</v>
@@ -8214,26 +8214,26 @@
         <v>-0.077501</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.147411</v>
+        <v>-0.147417</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.166162</v>
+        <v>-0.166302</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.277163</v>
+        <v>-0.277623</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.194576</v>
+        <v>-0.195219</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.38568</v>
+        <v>-0.387506</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.565689</v>
+        <v>-0.5701079999999999</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-1.690236</v>
+        <v>-1.721009</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8345,23 +8345,23 @@
         <v>0.121163</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.103855</v>
+        <v>0.103941</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.130853</v>
+        <v>0.131041</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058724</v>
+        <v>0.058852</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.088542</v>
+        <v>0.088793</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.073294</v>
+        <v>0.07348399999999999</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.08862</v>
+        <v>0.088835</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9000,20 +9000,20 @@
         <v>-0.153909</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>-0.137112</v>
+        <v>-0.138026</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>-0.194737</v>
+        <v>-0.195614</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.195166</v>
+        <v>-0.196061</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>-0.137632</v>
+        <v>-0.139557</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>-0.033898</v>
+        <v>-0.036055</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9417,23 +9417,23 @@
         <v>0.086462</v>
       </c>
       <c r="AG43" s="24" t="n">
+        <v>0.086463</v>
+      </c>
+      <c r="AH43" s="24" t="n">
+        <v>0.08645899999999999</v>
+      </c>
+      <c r="AI43" s="24" t="n">
         <v>0.086461</v>
-      </c>
-      <c r="AH43" s="24" t="n">
-        <v>0.086462</v>
-      </c>
-      <c r="AI43" s="24" t="n">
-        <v>0.086462</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.086463</v>
+        <v>0.086461</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.086461</v>
+        <v>0.086462</v>
       </c>
       <c r="AM43" s="24" t="n">
         <v>0.086461</v>

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$94</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$103</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$92</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 117168억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 119542억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 133026억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 142294억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 150036억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 157217억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 151360억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 151017억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 149619억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+2.4%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−3) 147411억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)</t>
+전년동기 × (1+2.4%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -768,121 +768,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.6% 유지</t>
+최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -894,55 +894,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1588억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1568억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1821억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1765억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1956억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1913억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2192억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2084억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2420억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2245억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2738억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2457억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2899억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2617억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3156억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2800억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3388억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2969억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1797,61 +1797,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 117168억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 119542억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 133026억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 142294억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+9.7%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 150036억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 157217억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 151360억 × 비례계수 0.0825 × 계절비중 Q1 0.174(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 151017억 × 비례계수 0.0825 × 계절비중 Q2 0.267(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+4.8%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 149619억 × 비례계수 0.0825 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+2.4%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−3) 147411억 × 비례계수 0.0825 × 계절비중 Q4 0.315(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=13, 창 19)
+        <t>추정: 전년동기 × (1+2.4%) — g=최근 4분기 합 YoY 9.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
@@ -2037,61 +2037,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
@@ -2192,61 +2192,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.6% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.6% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
@@ -2258,55 +2258,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1588억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1568억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1821억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1765억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1956억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1913억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2192억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2084억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2420억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2245억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2738억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2457억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2899억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2617억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3156억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2800억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3388억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2969억 × 2.06% − 총차입금 3432억 × 3.74% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4339,7 +4339,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4460,14 +4460,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 20.9% &gt; 추세 12.0% × 1.10 (suppliers_mentions·시차 3·4분기 이동합·창 19, r=0.99 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 20.9, "op_wape_pct": 48.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 2341.43, "rev_act": 1920.66, "op_pred": 140.4, "op_act": 154.26}, {"q": "2025Q4", "rev_pred": 3267.26, "rev_act": 2444.82, "op_pred": 195.91, "op_act": 53.68}, {"q": "2026Q1", "rev_pred": 1903.72, "rev_act": 1890.11, "op_pred": 114.15, "op_act": 175.04}, {"q": "2026Q2", "rev_pred": 2628.38, "rev_act": 2129.9, "op_pred": 157.6, "op_act": 249.61}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 12.0, "op_wape_pct": 47.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 20.8, "wape_trend": 9.2, "adopted": false}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 2237.33, "rev_act": 1920.66, "op_pred": 134.15, "op_act": 154.26}, {"q": "2025Q4", "rev_pred": 2511.93, "rev_act": 2444.82, "op_pred": 150.62, "op_act": 53.68}, {"q": "2026Q1", "rev_pred": 1604.91, "rev_act": 1890.11, "op_pred": 96.23, "op_act": 175.04}, {"q": "2026Q2", "rev_pred": 2464.41, "rev_act": 2129.9, "op_pred": 147.77, "op_act": 249.61}]}</t>
         </is>
       </c>
     </row>
@@ -6515,36 +6515,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.225955</v>
+        <v>0.096807</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.271577</v>
+        <v>0.096803</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.008854000000000001</v>
+        <v>0.096807</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.474019</v>
+        <v>0.096804</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.280523</v>
+        <v>0.0484</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.31516</v>
+        <v>0.048402</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.137825</v>
+        <v>0.048401</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.061306</v>
+        <v>0.048402</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.002783</v>
+        <v>0.024201</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.062372</v>
+        <v>0.024203</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6661,42 +6661,42 @@
         <v/>
       </c>
       <c r="AC22" s="24" t="n">
+        <v>0.078781</v>
+      </c>
+      <c r="AD22" s="24" t="n">
         <v>0.07878499999999999</v>
-      </c>
-      <c r="AD22" s="24" t="n">
-        <v>0.07878400000000001</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.07878499999999999</v>
+        <v>0.078781</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.07878300000000001</v>
+        <v>0.078782</v>
       </c>
       <c r="AH22" s="24" t="n">
         <v>0.07878499999999999</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.07878400000000001</v>
+        <v>0.07878300000000001</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.078782</v>
+        <v>0.07878400000000001</v>
       </c>
       <c r="AL22" s="24" t="n">
         <v>0.078782</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.078782</v>
+        <v>0.07878400000000001</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.07878400000000001</v>
+        <v>0.07878300000000001</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6816,42 +6816,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.08645899999999999</v>
+        <v>0.086462</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.086462</v>
+        <v>0.08646</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.086462</v>
+        <v>0.086461</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.086463</v>
+        <v>0.086461</v>
       </c>
       <c r="AH23" s="24" t="n">
         <v>0.08645899999999999</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.086461</v>
+        <v>0.086463</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.086461</v>
+        <v>0.086463</v>
       </c>
       <c r="AL23" s="24" t="n">
+        <v>0.086463</v>
+      </c>
+      <c r="AM23" s="24" t="n">
+        <v>0.08645899999999999</v>
+      </c>
+      <c r="AN23" s="24" t="n">
         <v>0.086462</v>
-      </c>
-      <c r="AM23" s="24" t="n">
-        <v>0.086461</v>
-      </c>
-      <c r="AN23" s="24" t="n">
-        <v>0.086461</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7093,39 +7093,39 @@
         <v>-24.81</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>-23.93</v>
+        <v>-24.04</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>-22.73</v>
+        <v>-23.02</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>-22.03</v>
+        <v>-22.25</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>-20.81</v>
+        <v>-21.37</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>-19.64</v>
+        <v>-20.54</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>-18</v>
+        <v>-19.45</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>-17.17</v>
+        <v>-18.62</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>-15.84</v>
+        <v>-17.68</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-14.64</v>
+        <v>-16.8</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7400,42 +7400,42 @@
         <v/>
       </c>
       <c r="AC27" s="24" t="n">
-        <v>0.050006</v>
+        <v>0.050022</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.049988</v>
+        <v>0.049998</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.050021</v>
+        <v>0.049994</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.049998</v>
+        <v>0.050019</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.049983</v>
+        <v>0.050006</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.049991</v>
+        <v>0.050016</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.050003</v>
+        <v>0.049979</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.050015</v>
+        <v>0.050018</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.050014</v>
+        <v>0.049972</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.049998</v>
+        <v>0.050013</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7820,36 +7820,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>0.0031</v>
+        <v>-0.0069</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -7948,36 +7948,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>0.0031</v>
+        <v>-0.0069</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8204,36 +8204,36 @@
         <v/>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>-0.07918699999999999</v>
+        <v>-0.069689</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>-0.117786</v>
+        <v>-0.098943</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>-0.077501</v>
+        <v>-0.082547</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.147417</v>
+        <v>-0.103512</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.166302</v>
+        <v>-0.108945</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.277623</v>
+        <v>-0.16044</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.195219</v>
+        <v>-0.144681</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.387506</v>
+        <v>-0.193906</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.5701079999999999</v>
+        <v>-0.221591</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-1.721009</v>
+        <v>-0.37145</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8332,36 +8332,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.119769</v>
+        <v>0.105397</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.146488</v>
+        <v>0.125943</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.074171</v>
+        <v>0.084087</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.121163</v>
+        <v>0.089241</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.103941</v>
+        <v>0.07729900000000001</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.131041</v>
+        <v>0.094156</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058852</v>
+        <v>0.065147</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.088793</v>
+        <v>0.07012</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.07348399999999999</v>
+        <v>0.060354</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.088835</v>
+        <v>0.074278</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8984,36 +8984,36 @@
         <v/>
       </c>
       <c r="AC40" s="24" t="n">
-        <v>-0.297885</v>
+        <v>-0.277301</v>
       </c>
       <c r="AD40" s="24" t="n">
-        <v>-0.407367</v>
+        <v>-0.362405</v>
       </c>
       <c r="AE40" s="25" t="n"/>
       <c r="AF40" s="24" t="n">
-        <v>-0.379761</v>
+        <v>-0.343308</v>
       </c>
       <c r="AG40" s="24" t="n">
-        <v>-0.546856</v>
+        <v>-0.473022</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>-0.153909</v>
+        <v>0.009494000000000001</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>-0.138026</v>
+        <v>0.062872</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>-0.195614</v>
+        <v>0.019056</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.196061</v>
+        <v>-0.07005400000000001</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>-0.139557</v>
+        <v>-0.06347999999999999</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>-0.036055</v>
+        <v>-0.056755</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9103,36 +9103,36 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-0.44757</v>
+        <v>-0.445013</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>-0.506053</v>
+        <v>-0.498789</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>-0.483029</v>
+        <v>-0.477807</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.56682</v>
+        <v>-0.557604</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.171296</v>
+        <v>-0.142857</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.176471</v>
+        <v>-0.140097</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.176768</v>
+        <v>-0.14</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.175532</v>
+        <v>-0.135417</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.167598</v>
+        <v>-0.134409</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.154762</v>
+        <v>-0.134831</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9404,42 +9404,42 @@
         <v/>
       </c>
       <c r="AC43" s="24" t="n">
-        <v>0.08645899999999999</v>
+        <v>0.086462</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.086462</v>
+        <v>0.08646</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
-        <v>0.086462</v>
+        <v>0.086461</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.086463</v>
+        <v>0.086461</v>
       </c>
       <c r="AH43" s="24" t="n">
         <v>0.08645899999999999</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.086461</v>
+        <v>0.086463</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.086461</v>
+        <v>0.086463</v>
       </c>
       <c r="AL43" s="24" t="n">
+        <v>0.086463</v>
+      </c>
+      <c r="AM43" s="24" t="n">
+        <v>0.08645899999999999</v>
+      </c>
+      <c r="AN43" s="24" t="n">
         <v>0.086462</v>
-      </c>
-      <c r="AM43" s="24" t="n">
-        <v>0.086461</v>
-      </c>
-      <c r="AN43" s="24" t="n">
-        <v>0.086461</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -9934,7 +9934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO94"/>
+  <dimension ref="A1:AO103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16823,78 +16823,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>10623</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>22413</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>-15740</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>-17870</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>37775</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>26578</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>-29292</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>14728</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>-20107</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>21394</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>-13277</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>-12374</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>-17487</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>-1349</v>
-      </c>
-      <c r="T79" s="18" t="n">
-        <v>67922.2</v>
-      </c>
-      <c r="U79" s="34" t="n">
-        <v>36712.2</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="U79" s="9" t="n"/>
       <c r="V79" s="18" t="n">
-        <v>-46156.78</v>
+        <v>576.6799999999999</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>59531.99</v>
+        <v>400.92</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>58318.39</v>
+        <v>922.1</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>1177.45</v>
+        <v>987.34</v>
       </c>
       <c r="Z79" s="34" t="n">
-        <v>72871.05</v>
+        <v>2887.04</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>-76331.59</v>
+        <v>1064.78</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>19318.66</v>
+        <v>789.85</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -16916,78 +16871,33 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>123</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>179</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>199</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>263</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>406</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>1047</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>562</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>681</v>
-      </c>
-      <c r="N80" s="18" t="n">
-        <v>490</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>540</v>
-      </c>
-      <c r="P80" s="34" t="n">
-        <v>2273</v>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>755</v>
-      </c>
-      <c r="R80" s="18" t="n">
-        <v>850</v>
-      </c>
-      <c r="S80" s="18" t="n">
-        <v>821</v>
-      </c>
-      <c r="T80" s="18" t="n">
-        <v>766.36</v>
-      </c>
-      <c r="U80" s="34" t="n">
-        <v>3192.36</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
+      <c r="U80" s="9" t="n"/>
       <c r="V80" s="18" t="n">
-        <v>708.77</v>
+        <v>3462.5</v>
       </c>
       <c r="W80" s="18" t="n">
-        <v>519.1</v>
+        <v>3010.97</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>796.51</v>
+        <v>3040.12</v>
       </c>
       <c r="Y80" s="18" t="n">
-        <v>934.38</v>
+        <v>3046.07</v>
       </c>
       <c r="Z80" s="34" t="n">
-        <v>2958.76</v>
+        <v>12559.66</v>
       </c>
       <c r="AA80" s="18" t="n">
-        <v>790.1</v>
+        <v>2998.65</v>
       </c>
       <c r="AB80" s="19" t="n">
-        <v>814.35</v>
+        <v>3144.86</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -17009,78 +16919,33 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>-19</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>-233</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>-235</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>-167</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>-684</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>-403</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>-578</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>-74</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>485</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>-570</v>
-      </c>
-      <c r="Q81" s="18" t="n">
-        <v>-987</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>-151</v>
-      </c>
-      <c r="S81" s="18" t="n">
-        <v>458</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>-126.56</v>
-      </c>
-      <c r="U81" s="34" t="n">
-        <v>-806.5599999999999</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
+      <c r="U81" s="9" t="n"/>
       <c r="V81" s="18" t="n">
-        <v>-579.24</v>
+        <v>5809.42</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>-199.74</v>
+        <v>3862.33</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>-181.13</v>
+        <v>3295.81</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>-404.22</v>
+        <v>3510.15</v>
       </c>
       <c r="Z81" s="34" t="n">
-        <v>-1364.33</v>
+        <v>16477.71</v>
       </c>
       <c r="AA81" s="18" t="n">
-        <v>-718.13</v>
+        <v>3089.73</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>-437.46</v>
+        <v>3226.71</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -17102,78 +16967,33 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>-4004</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-1864</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>-1747</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>-1328</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-10286</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-15225</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>-2713</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>2675</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>7226</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>-3524</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>3664</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>-1304</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>-2574</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>-4842</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>-6178.13</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>-14898.13</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
       <c r="V82" s="18" t="n">
-        <v>-3405.46</v>
+        <v>6418.45</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-3982.16</v>
+        <v>6115.47</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>-8356.719999999999</v>
+        <v>3773.07</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>-10864.63</v>
+        <v>5374.45</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>-26608.97</v>
+        <v>21681.44</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>-12043.6</v>
+        <v>2962.93</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>-3810.84</v>
+        <v>4245.05</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -17195,52 +17015,34 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>2</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="H83" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>41</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>134</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
+      <c r="V83" s="18" t="n">
+        <v>437.15</v>
+      </c>
+      <c r="W83" s="18" t="n">
+        <v>517.77</v>
+      </c>
       <c r="X83" s="18" t="n">
-        <v>0</v>
+        <v>-32.47</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="9" t="n"/>
-      <c r="AB83" s="5" t="n"/>
+        <v>506.15</v>
+      </c>
+      <c r="Z83" s="34" t="n">
+        <v>1428.6</v>
+      </c>
+      <c r="AA83" s="18" t="n">
+        <v>1833.46</v>
+      </c>
+      <c r="AB83" s="19" t="n">
+        <v>-339.54</v>
+      </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
       <c r="AE83" s="11" t="n"/>
@@ -17261,21 +17063,34 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>0</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="K84" s="9" t="n"/>
-      <c r="O84" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="P84" s="9" t="n"/>
       <c r="U84" s="9" t="n"/>
-      <c r="Z84" s="9" t="n"/>
-      <c r="AB84" s="5" t="n"/>
+      <c r="V84" s="18" t="n">
+        <v>4165.37</v>
+      </c>
+      <c r="W84" s="18" t="n">
+        <v>-558.36</v>
+      </c>
+      <c r="X84" s="18" t="n">
+        <v>170.33</v>
+      </c>
+      <c r="Y84" s="18" t="n">
+        <v>-1258.24</v>
+      </c>
+      <c r="Z84" s="34" t="n">
+        <v>2519.1</v>
+      </c>
+      <c r="AA84" s="18" t="n">
+        <v>3044.6</v>
+      </c>
+      <c r="AB84" s="19" t="n">
+        <v>528.01</v>
+      </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
       <c r="AE84" s="11" t="n"/>
@@ -17296,78 +17111,33 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>4056</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>2839</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>1627</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>6375</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>12191</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>2140</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>1654</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>2441</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>2452</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>8687</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>1497</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>1154</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>2444</v>
-      </c>
-      <c r="T85" s="18" t="n">
-        <v>4076.71</v>
-      </c>
-      <c r="U85" s="34" t="n">
-        <v>9171.709999999999</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
       <c r="V85" s="18" t="n">
-        <v>1803.95</v>
+        <v>2084.44</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>2075.63</v>
+        <v>439.39</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>2292.47</v>
+        <v>1274.73</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>3740.95</v>
+        <v>1191.65</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>9913</v>
+        <v>4990.21</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>4123.91</v>
+        <v>1261.37</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>3655.7</v>
+        <v>1327.25</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -17389,78 +17159,33 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>4352</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>2845</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>1872</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>1351</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>6613</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>12681</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>2346</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>5924</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>2814</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>4855</v>
-      </c>
-      <c r="P86" s="34" t="n">
-        <v>15939</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>1691</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>2529</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>4840</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>9289.530000000001</v>
-      </c>
-      <c r="U86" s="34" t="n">
-        <v>18349.53</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
       <c r="V86" s="18" t="n">
-        <v>3348.64</v>
+        <v>100.87</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>2805.15</v>
+        <v>136.47</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>6618.52</v>
+        <v>-136.47</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>6193.4</v>
+        <v>365.37</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>18965.71</v>
+        <v>466.24</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>4193.54</v>
+        <v>0</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>4460.18</v>
+        <v>0</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -17482,78 +17207,33 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>296</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>245</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>238</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>490</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>206</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>4270</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>373</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>2403</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>7252</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>194</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>1375</v>
-      </c>
-      <c r="S87" s="18" t="n">
-        <v>2396</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>5212.82</v>
-      </c>
-      <c r="U87" s="34" t="n">
-        <v>9177.82</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="U87" s="9" t="n"/>
       <c r="V87" s="18" t="n">
-        <v>1544.69</v>
+        <v>-2885.82</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>729.52</v>
+        <v>-2610.05</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>4326.05</v>
+        <v>-2118.02</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>2452.45</v>
+        <v>-2058.73</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>9052.709999999999</v>
+        <v>-9672.620000000001</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>69.63</v>
+        <v>-1933.87</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>804.48</v>
+        <v>-2355.01</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -17575,78 +17255,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>-4942</v>
+        <v>10623</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>-15747</v>
+        <v>22413</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>-15216</v>
+        <v>-15740</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>-1336</v>
+        <v>-17870</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>4482</v>
+        <v>37775</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>-27817</v>
+        <v>26578</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>6953</v>
+        <v>-29292</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>-9276</v>
+        <v>14728</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>-819</v>
+        <v>-20107</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>10922</v>
+        <v>21394</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>7780</v>
+        <v>-13277</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>31980</v>
+        <v>-12374</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>16235</v>
+        <v>-17487</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>3587</v>
+        <v>-1349</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>-29864</v>
+        <v>67922.2</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>21938</v>
+        <v>36712.2</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>-37647.71</v>
+        <v>-46156.78</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>9555.040000000001</v>
+        <v>59531.99</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>7400.18</v>
+        <v>58318.39</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>6846.89</v>
+        <v>1177.45</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>-13845.6</v>
+        <v>72871.05</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>33688.69</v>
+        <v>-76331.59</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>-11849.37</v>
+        <v>19318.66</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -17668,78 +17348,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>차입금의증가</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>20587</v>
+        <v>123</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>16172</v>
+        <v>179</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>16355</v>
+        <v>199</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>27368</v>
+        <v>263</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>42367</v>
+        <v>406</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>102262</v>
+        <v>1047</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>31430</v>
+        <v>562</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>17223</v>
+        <v>681</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>27781</v>
+        <v>490</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>39836</v>
+        <v>540</v>
       </c>
       <c r="P89" s="34" t="n">
-        <v>116270</v>
+        <v>2273</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>57603</v>
+        <v>755</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>45824</v>
+        <v>850</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>54976</v>
+        <v>821</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>39763.36</v>
+        <v>766.36</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>198166.36</v>
+        <v>3192.36</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>31485.56</v>
+        <v>708.77</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>66430.27</v>
+        <v>519.1</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>48797.62</v>
+        <v>796.51</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>53985.05</v>
+        <v>934.38</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>200698.5</v>
+        <v>2958.76</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>55996.23</v>
+        <v>790.1</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>70864.23</v>
+        <v>814.35</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -17761,78 +17441,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>23472</v>
+        <v>-19</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>29714</v>
+        <v>-49</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>29251</v>
+        <v>-233</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>26233</v>
+        <v>-235</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>36891</v>
+        <v>-167</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>122089</v>
+        <v>-684</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>21774</v>
+        <v>-403</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>23278</v>
+        <v>-578</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>26088</v>
+        <v>-74</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>23959</v>
+        <v>485</v>
       </c>
       <c r="P90" s="34" t="n">
-        <v>95099</v>
+        <v>-570</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>20037</v>
+        <v>-987</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>23849</v>
+        <v>-151</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>46830</v>
+        <v>458</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>62068.43</v>
+        <v>-126.56</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>152784.43</v>
+        <v>-806.5599999999999</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>61680.16</v>
+        <v>-579.24</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>53031.07</v>
+        <v>-199.74</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>38603.34</v>
+        <v>-181.13</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>47787.13</v>
+        <v>-404.22</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>201101.7</v>
+        <v>-1364.33</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>19778.46</v>
+        <v>-718.13</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>80909.11</v>
+        <v>-437.46</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -17854,73 +17534,78 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>350</v>
+        <v>-4004</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>354</v>
+        <v>-1864</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>330</v>
+        <v>-1747</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>788</v>
-      </c>
-      <c r="K91" s="9" t="n"/>
+        <v>-1328</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>-10286</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>-15225</v>
+      </c>
       <c r="L91" s="18" t="n">
-        <v>409</v>
+        <v>-2713</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>411</v>
+        <v>2675</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>434</v>
+        <v>7226</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>438</v>
+        <v>-3524</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>1692</v>
+        <v>3664</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>425</v>
+        <v>-1304</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>404</v>
+        <v>-2574</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>463</v>
+        <v>-4842</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>468.43</v>
+        <v>-6178.13</v>
       </c>
       <c r="U91" s="34" t="n">
-        <v>1760.43</v>
+        <v>-14898.13</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>482.26</v>
+        <v>-3405.46</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>472.72</v>
+        <v>-3982.16</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>494.78</v>
+        <v>-8356.719999999999</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>499.92</v>
+        <v>-10864.63</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>1949.68</v>
+        <v>-26608.97</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>505.42</v>
+        <v>-12043.6</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>514.65</v>
+        <v>-3810.84</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -17942,79 +17627,52 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>-1506</v>
+        <v>2</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>-1616</v>
+        <v>16</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>-1787</v>
+        <v>1</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>-1911</v>
+        <v>0</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>-2401</v>
+        <v>0</v>
       </c>
       <c r="K92" s="34" t="n">
-        <v>-7715</v>
+        <v>17</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>-2632</v>
+        <v>8</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>-2707</v>
+        <v>49</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>-2577</v>
+        <v>41</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>-4377</v>
+        <v>36</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>-12293</v>
-      </c>
-      <c r="Q92" s="18" t="n">
-        <v>-3486</v>
-      </c>
-      <c r="R92" s="18" t="n">
-        <v>-3471</v>
-      </c>
-      <c r="S92" s="18" t="n">
-        <v>-3891</v>
-      </c>
-      <c r="T92" s="18" t="n">
-        <v>-4378.41</v>
-      </c>
-      <c r="U92" s="34" t="n">
-        <v>-15226.41</v>
-      </c>
-      <c r="V92" s="18" t="n">
-        <v>-4699.27</v>
-      </c>
-      <c r="W92" s="18" t="n">
-        <v>-3804.76</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="U92" s="9" t="n"/>
       <c r="X92" s="18" t="n">
-        <v>-3280.91</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>-3637.66</v>
-      </c>
-      <c r="Z92" s="34" t="n">
-        <v>-15422.6</v>
-      </c>
-      <c r="AA92" s="18" t="n">
-        <v>-2387.88</v>
-      </c>
-      <c r="AB92" s="19" t="n">
-        <v>-3035.56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z92" s="9" t="n"/>
+      <c r="AB92" s="5" t="n"/>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -18035,79 +17693,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>1635</v>
+        <v>0</v>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>4830</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>-32628</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>-20241</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>31629</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>-16410</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>-24865</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>8104</v>
-      </c>
-      <c r="N93" s="18" t="n">
-        <v>-13605</v>
-      </c>
+      <c r="K93" s="9" t="n"/>
       <c r="O93" s="18" t="n">
-        <v>28705</v>
-      </c>
-      <c r="P93" s="34" t="n">
-        <v>-1661</v>
-      </c>
-      <c r="Q93" s="18" t="n">
-        <v>18596</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>-3516</v>
-      </c>
-      <c r="S93" s="18" t="n">
-        <v>-3208</v>
-      </c>
-      <c r="T93" s="18" t="n">
-        <v>31880.07</v>
-      </c>
-      <c r="U93" s="34" t="n">
-        <v>43752.07</v>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>-87209.95</v>
-      </c>
-      <c r="W93" s="18" t="n">
-        <v>65104.87</v>
-      </c>
-      <c r="X93" s="18" t="n">
-        <v>57361.85</v>
-      </c>
-      <c r="Y93" s="18" t="n">
-        <v>-2840.29</v>
-      </c>
-      <c r="Z93" s="34" t="n">
-        <v>32416.48</v>
-      </c>
-      <c r="AA93" s="18" t="n">
-        <v>-54686.5</v>
-      </c>
-      <c r="AB93" s="19" t="n">
-        <v>3658.45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P93" s="9" t="n"/>
+      <c r="U93" s="9" t="n"/>
+      <c r="Z93" s="9" t="n"/>
+      <c r="AB93" s="5" t="n"/>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="11" t="n"/>
@@ -18128,78 +17728,78 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>1635</v>
+        <v>4056</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="18" t="n">
-        <v>109517</v>
+        <v>2839</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>-32628</v>
+        <v>1627</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>-20241</v>
+        <v>1350</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>31629</v>
+        <v>6375</v>
       </c>
       <c r="K94" s="34" t="n">
-        <v>88277</v>
+        <v>12191</v>
       </c>
       <c r="L94" s="18" t="n">
-        <v>63412</v>
+        <v>2140</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>8104</v>
+        <v>1654</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>-13605</v>
+        <v>2441</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>28705</v>
+        <v>2452</v>
       </c>
       <c r="P94" s="34" t="n">
-        <v>86616</v>
+        <v>8687</v>
       </c>
       <c r="Q94" s="18" t="n">
-        <v>105211</v>
+        <v>1497</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>-3516</v>
+        <v>1154</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>-3076</v>
+        <v>2444</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>32821.92</v>
+        <v>4076.71</v>
       </c>
       <c r="U94" s="34" t="n">
-        <v>131440.92</v>
+        <v>9171.709999999999</v>
       </c>
       <c r="V94" s="18" t="n">
-        <v>44331.39</v>
+        <v>1803.95</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>64684.67</v>
+        <v>2075.63</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>58133.15</v>
+        <v>2292.47</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>-3014.88</v>
+        <v>3740.95</v>
       </c>
       <c r="Z94" s="34" t="n">
-        <v>164134.33</v>
+        <v>9913</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>110270.44</v>
+        <v>4123.91</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>3964.92</v>
+        <v>3655.7</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -18214,6 +17814,838 @@
       <c r="AM94" s="10" t="n"/>
       <c r="AN94" s="10" t="n"/>
       <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>4352</v>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>2845</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>1872</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>1351</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>6613</v>
+      </c>
+      <c r="K95" s="34" t="n">
+        <v>12681</v>
+      </c>
+      <c r="L95" s="18" t="n">
+        <v>2346</v>
+      </c>
+      <c r="M95" s="18" t="n">
+        <v>5924</v>
+      </c>
+      <c r="N95" s="18" t="n">
+        <v>2814</v>
+      </c>
+      <c r="O95" s="18" t="n">
+        <v>4855</v>
+      </c>
+      <c r="P95" s="34" t="n">
+        <v>15939</v>
+      </c>
+      <c r="Q95" s="18" t="n">
+        <v>1691</v>
+      </c>
+      <c r="R95" s="18" t="n">
+        <v>2529</v>
+      </c>
+      <c r="S95" s="18" t="n">
+        <v>4840</v>
+      </c>
+      <c r="T95" s="18" t="n">
+        <v>9289.530000000001</v>
+      </c>
+      <c r="U95" s="34" t="n">
+        <v>18349.53</v>
+      </c>
+      <c r="V95" s="18" t="n">
+        <v>3348.64</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>2805.15</v>
+      </c>
+      <c r="X95" s="18" t="n">
+        <v>6618.52</v>
+      </c>
+      <c r="Y95" s="18" t="n">
+        <v>6193.4</v>
+      </c>
+      <c r="Z95" s="34" t="n">
+        <v>18965.71</v>
+      </c>
+      <c r="AA95" s="18" t="n">
+        <v>4193.54</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>4460.18</v>
+      </c>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>296</v>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>245</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>238</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>490</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>206</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>4270</v>
+      </c>
+      <c r="N96" s="18" t="n">
+        <v>373</v>
+      </c>
+      <c r="O96" s="18" t="n">
+        <v>2403</v>
+      </c>
+      <c r="P96" s="34" t="n">
+        <v>7252</v>
+      </c>
+      <c r="Q96" s="18" t="n">
+        <v>194</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>1375</v>
+      </c>
+      <c r="S96" s="18" t="n">
+        <v>2396</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>5212.82</v>
+      </c>
+      <c r="U96" s="34" t="n">
+        <v>9177.82</v>
+      </c>
+      <c r="V96" s="18" t="n">
+        <v>1544.69</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>729.52</v>
+      </c>
+      <c r="X96" s="18" t="n">
+        <v>4326.05</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>2452.45</v>
+      </c>
+      <c r="Z96" s="34" t="n">
+        <v>9052.709999999999</v>
+      </c>
+      <c r="AA96" s="18" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="AB96" s="19" t="n">
+        <v>804.48</v>
+      </c>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>-4942</v>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>-15747</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>-15216</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>-1336</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>4482</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>-27817</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>6953</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>-9276</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>-819</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>10922</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>7780</v>
+      </c>
+      <c r="Q97" s="18" t="n">
+        <v>31980</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>16235</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>3587</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>-29864</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>21938</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>-37647.71</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>9555.040000000001</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>7400.18</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>6846.89</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>-13845.6</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>33688.69</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>-11849.37</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>차입금의증가</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>20587</v>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>16172</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>16355</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>27368</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>42367</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>102262</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>31430</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>17223</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>27781</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>39836</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>116270</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>57603</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>45824</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>54976</v>
+      </c>
+      <c r="T98" s="18" t="n">
+        <v>39763.36</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>198166.36</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>31485.56</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>66430.27</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>48797.62</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>53985.05</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>200698.5</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>55996.23</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>70864.23</v>
+      </c>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>차입금의감소</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>23472</v>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>29714</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>29251</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>26233</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>36891</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>122089</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>21774</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>23278</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>26088</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>23959</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>95099</v>
+      </c>
+      <c r="Q99" s="18" t="n">
+        <v>20037</v>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>23849</v>
+      </c>
+      <c r="S99" s="18" t="n">
+        <v>46830</v>
+      </c>
+      <c r="T99" s="18" t="n">
+        <v>62068.43</v>
+      </c>
+      <c r="U99" s="34" t="n">
+        <v>152784.43</v>
+      </c>
+      <c r="V99" s="18" t="n">
+        <v>61680.16</v>
+      </c>
+      <c r="W99" s="18" t="n">
+        <v>53031.07</v>
+      </c>
+      <c r="X99" s="18" t="n">
+        <v>38603.34</v>
+      </c>
+      <c r="Y99" s="18" t="n">
+        <v>47787.13</v>
+      </c>
+      <c r="Z99" s="34" t="n">
+        <v>201101.7</v>
+      </c>
+      <c r="AA99" s="18" t="n">
+        <v>19778.46</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>80909.11</v>
+      </c>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>350</v>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="18" t="n">
+        <v>354</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>330</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>788</v>
+      </c>
+      <c r="K100" s="9" t="n"/>
+      <c r="L100" s="18" t="n">
+        <v>409</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>411</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>434</v>
+      </c>
+      <c r="O100" s="18" t="n">
+        <v>438</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>1692</v>
+      </c>
+      <c r="Q100" s="18" t="n">
+        <v>425</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>404</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>463</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>468.43</v>
+      </c>
+      <c r="U100" s="34" t="n">
+        <v>1760.43</v>
+      </c>
+      <c r="V100" s="18" t="n">
+        <v>482.26</v>
+      </c>
+      <c r="W100" s="18" t="n">
+        <v>472.72</v>
+      </c>
+      <c r="X100" s="18" t="n">
+        <v>494.78</v>
+      </c>
+      <c r="Y100" s="18" t="n">
+        <v>499.92</v>
+      </c>
+      <c r="Z100" s="34" t="n">
+        <v>1949.68</v>
+      </c>
+      <c r="AA100" s="18" t="n">
+        <v>505.42</v>
+      </c>
+      <c r="AB100" s="19" t="n">
+        <v>514.65</v>
+      </c>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>-1506</v>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>-1616</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>-1787</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>-1911</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>-2401</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>-7715</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>-2632</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>-2707</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>-2577</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>-4377</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>-12293</v>
+      </c>
+      <c r="Q101" s="18" t="n">
+        <v>-3486</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>-3471</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>-3891</v>
+      </c>
+      <c r="T101" s="18" t="n">
+        <v>-4378.41</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>-15226.41</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>-4699.27</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>-3804.76</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>-3280.91</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>-3637.66</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>-15422.6</v>
+      </c>
+      <c r="AA101" s="18" t="n">
+        <v>-2387.88</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>-3035.56</v>
+      </c>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>1635</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>4830</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>-32628</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>-20241</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>31629</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>-16410</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>-24865</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>8104</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>-13605</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>28705</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>-1661</v>
+      </c>
+      <c r="Q102" s="18" t="n">
+        <v>18596</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>-3516</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>-3208</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>31880.07</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>43752.07</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>-87209.95</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>65104.87</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>57361.85</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>-2840.29</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>32416.48</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>-54686.5</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>3658.45</v>
+      </c>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>1635</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>109517</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>-32628</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>-20241</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>31629</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>88277</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>63412</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>8104</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>-13605</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>28705</v>
+      </c>
+      <c r="P103" s="34" t="n">
+        <v>86616</v>
+      </c>
+      <c r="Q103" s="18" t="n">
+        <v>105211</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>-3516</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>-3076</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>32821.92</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>131440.92</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>44331.39</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>64684.67</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>58133.15</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>-3014.88</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>164134.33</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>110270.44</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>3964.92</v>
+      </c>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18474,7 +18906,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39335,7 +39767,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1929.3</v>
+        <v>1659.3</v>
       </c>
     </row>
     <row r="30">
@@ -39355,7 +39787,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.17</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="32">
@@ -39375,7 +39807,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2022</v>
+        <v>0.1739</v>
       </c>
     </row>
     <row r="34">
@@ -39385,7 +39817,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="35">
@@ -39395,7 +39827,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>21500</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>22750</v>
+        <v>23050</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6194,7 +6194,7 @@
         <v>31550</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>22900</v>
+        <v>23250</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>22700</v>
+        <v>22816.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>22750</v>
+        <v>23050</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07878301633839889</v>
+        <v>0.07878301633839888</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02327319820050878</v>
+        <v>0.02327319820050917</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.0370842311238601</v>
+        <v>0.03708423112386032</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.59</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="32">
@@ -40709,7 +40709,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>23050</v>
+        <v>22150</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6194,7 +6194,7 @@
         <v>31550</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>23250</v>
+        <v>23800</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>22816.7</v>
+        <v>22662.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9258,11 +9258,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>23050</v>
+        <v>22150</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 22,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 22,650원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.81</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="32">
@@ -40709,7 +40709,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>22150</v>
+        <v>20750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>18830</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>21750</v>
+        <v>20550</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>22662.5</v>
+        <v>22270</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9258,11 +9258,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>22150</v>
+        <v>20750</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 22,650원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 23,100원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.15</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="32">
@@ -40709,7 +40709,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1076,62 +1076,62 @@
     </comment>
     <comment ref="AC28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0(r4)
+max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AD28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0(r4)
+max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AF28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0275(r4)
+max(세전, 0) × 세율 2.8%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AG28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.055(r4)
+max(세전, 0) × 세율 5.5%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AH28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0825(r4)
+max(세전, 0) × 세율 8.2%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AI28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.11(r4)
+max(세전, 0) × 세율 11.0%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AK28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1375(r4)
+max(세전, 0) × 세율 13.8%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AL28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.165(r4)
+max(세전, 0) × 세율 16.5%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AM28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1925(r4)
+max(세전, 0) × 세율 19.2%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AN28" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.22(r4)
+max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AC29" authorId="0" shapeId="0">
@@ -2070,55 +2070,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1542억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1577억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1705억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1786억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1827억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1939억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1968억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2111억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2102억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2268억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2276억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2468억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2408억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2615억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2559억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2778억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2699억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2923억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2130,55 +2130,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1542억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1577억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1705억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1786억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1827억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1939억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1968억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2111억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2102억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2268억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2276억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2468억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2408억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2615억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2559억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2778억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2699억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2923억 × 2.33%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 3432억 × 3.71%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2544,61 +2544,61 @@
     </comment>
     <comment ref="AC18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AD18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AF18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 2.8%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AG18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 5.5%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AH18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 8.2%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AI18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 11.0%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AK18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 13.8%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AL18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 16.5%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AM18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 19.2%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AN18" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 0% → 22%(terminal, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프) — 이월결손 램프(assumptions.tax_schedule): 변수 drv:법인세비용 추정 분기 셀이 분기별 세율(3절 '세율' 스칼라 연결 안 됨 — 그 값은 시작 세율) · 근거: 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(이월결손 램프(assumptions.tax_schedule, 0%→22%) — 분기별 세율 드라이버 행 사용)</t>
         </is>
       </c>
     </row>
@@ -4465,14 +4465,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 20.9% &gt; 추세 12.0% × 1.10 (suppliers_mentions·시차 3·4분기 이동합·창 19, r=0.99 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 20.9% &gt; 추세 12.0% × 1.10 (suppliers_mentions·시차 3·4분기 이동합·창 19, r=0.99 유의)): 전년동기 × (1+g) 추세 / 법인세율 이월결손 경로: 최근 양(+)세전 8분기 유효세율 중위 -3.3% → 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 12.0, "op_wape_pct": 47.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 20.8, "wape_trend": 9.2, "adopted": false, "decision": "rejected"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 2237.33, "rev_act": 1920.66, "op_pred": 134.15, "op_act": 154.26}, {"q": "2025Q4", "rev_pred": 2511.93, "rev_act": 2444.82, "op_pred": 150.62, "op_act": 53.68}, {"q": "2026Q1", "rev_pred": 1604.91, "rev_act": 1890.11, "op_pred": 96.23, "op_act": 175.04}, {"q": "2026Q2", "rev_pred": 2464.41, "rev_act": 2129.9, "op_pred": 147.77, "op_act": 249.61}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 20.9, "op_wape_pct": 48.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": 9.2, "adopted": "undetermined", "decision": "undetermined", "note": "현재 채택 조합(suppliers_mentions·시차 3·ma4·창 12)을 동결 데이터로 재적합할 수 없음(짝·고객 모델 부족) → 연동 WAPE 없음, undetermined(유의성 조건만으로 채택)"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 2341.43, "rev_act": 1920.66, "op_pred": 140.4, "op_act": 154.26}, {"q": "2025Q4", "rev_pred": 3267.26, "rev_act": 2444.82, "op_pred": 195.91, "op_act": 53.68}, {"q": "2026Q1", "rev_pred": 1903.72, "rev_act": 1890.11, "op_pred": 114.15, "op_act": 175.04}, {"q": "2026Q2", "rev_pred": 2628.38, "rev_act": 2129.9, "op_pred": 157.6, "op_act": 249.61}]}</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 세율</t>
+          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 분기별 세율(이월결손 램프, assumptions.tax_schedule)</t>
         </is>
       </c>
       <c r="E28" s="21">
@@ -7613,53 +7613,43 @@
         <f>IFERROR(subQ!AB18/subQ!AB17,"")</f>
         <v/>
       </c>
-      <c r="AC28" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AD28" s="26">
-        <f>$D$50</f>
-        <v/>
+      <c r="AC28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE18/subQ!AE17,"")</f>
         <v/>
       </c>
-      <c r="AF28" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AG28" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AH28" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AI28" s="26">
-        <f>$D$50</f>
-        <v/>
+      <c r="AF28" s="24" t="n">
+        <v>0.027501426</v>
+      </c>
+      <c r="AG28" s="24" t="n">
+        <v>0.055004409</v>
+      </c>
+      <c r="AH28" s="24" t="n">
+        <v>0.08249227000000001</v>
+      </c>
+      <c r="AI28" s="24" t="n">
+        <v>0.110007129</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ18/subQ!AJ17,"")</f>
         <v/>
       </c>
-      <c r="AK28" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AL28" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AM28" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AN28" s="26">
-        <f>$D$50</f>
-        <v/>
+      <c r="AK28" s="24" t="n">
+        <v>0.137518334</v>
+      </c>
+      <c r="AL28" s="24" t="n">
+        <v>0.165001281</v>
+      </c>
+      <c r="AM28" s="24" t="n">
+        <v>0.192474433</v>
+      </c>
+      <c r="AN28" s="24" t="n">
+        <v>0.219996583</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO18/subQ!AO17,"")</f>
@@ -8054,36 +8044,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.009281819</v>
+        <v>0.001220222</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.006063628</v>
+        <v>0.0008671660000000001</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.005230261</v>
+        <v>-0.00160795</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.009589881999999999</v>
+        <v>0.001357101</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.003918981</v>
+        <v>-0.000606389</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.004045721</v>
+        <v>0.004095056</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.007552835</v>
+        <v>-0.003889981</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.002446145</v>
+        <v>0.002249301</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.0006061350000000001</v>
+        <v>0.0027428</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-7.082799999999999e-05</v>
+        <v>-0.002731924</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8182,36 +8172,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.009281819</v>
+        <v>0.001220222</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.006063628</v>
+        <v>0.0008671660000000001</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.005230261</v>
+        <v>-0.00160795</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.009589881999999999</v>
+        <v>0.001357101</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.003918981</v>
+        <v>-0.000606389</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.004045721</v>
+        <v>0.004095056</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.007552835</v>
+        <v>-0.003889981</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>0.002446145</v>
+        <v>0.002249301</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.0006061350000000001</v>
+        <v>0.0027428</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-7.082799999999999e-05</v>
+        <v>-0.002731924</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8438,36 +8428,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>-0.057664539</v>
+        <v>-0.07393204</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>-0.080659446</v>
+        <v>-0.10532172</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.06604702699999999</v>
+        <v>-0.086364174</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.081257383</v>
+        <v>-0.105608732</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.08345773200000001</v>
+        <v>-0.108306705</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.119285832</v>
+        <v>-0.154269738</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.102628655</v>
+        <v>-0.134257484</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.13099083</v>
+        <v>-0.171880933</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.138838792</v>
+        <v>-0.185048848</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.210131093</v>
+        <v>-0.285444116</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8566,36 +8556,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.087217286</v>
+        <v>0.111814101</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.105730501</v>
+        <v>0.132688075</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.071986673</v>
+        <v>0.08593203200000001</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.077166371</v>
+        <v>0.08841895700000001</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.067594615</v>
+        <v>0.07450870800000001</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.082938389</v>
+        <v>0.088072027</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.058039598</v>
+        <v>0.059575813</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.06282107200000001</v>
+        <v>0.062318342</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.054450184</v>
+        <v>0.052301323</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.067294901</v>
+        <v>0.062476266</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9533,11 +9523,11 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.2199905040837775</v>
+        <v>0</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.22) · 최근 12분기 유효세율 -7.6% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -3.3% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>참고(연결 안 됨: 이월결손 램프(assumptions.tax_schedule, 0%→22%) — 분기별 세율 드라이버 행 사용) — 모델 assumptions 값(시작 0% → terminal 22%, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프 — 분기별 값은 2절 drv:법인세비용 행) · 최근 8분기 중 세전 &gt; 0 인 8분기(2024Q3~2026Q2) 법인세/세전 중위 -3.3%·최근 4분기 중위 -1.8% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -9572,7 +9562,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07878301633839888</v>
+        <v>0.07878301633839889</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9650,7 +9640,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02327319820050917</v>
+        <v>0.02327875647844624</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9689,7 +9679,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03708423112386032</v>
+        <v>0.03708883192647326</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10126,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18850,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40679,7 +40669,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1371.2</v>
+        <v>1725.7</v>
       </c>
     </row>
     <row r="30">
@@ -40699,7 +40689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.13</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="32">
@@ -40719,7 +40709,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1437</v>
+        <v>0.1809</v>
       </c>
     </row>
     <row r="34">
@@ -40729,7 +40719,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="35">
@@ -40739,7 +40729,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15300</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>20750</v>
+        <v>20800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>22270</v>
+        <v>22280</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9248,11 +9248,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>20750</v>
+        <v>20800</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 23,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 22,100원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07878301633839889</v>
+        <v>0.07878301633839888</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02327875647844624</v>
+        <v>0.02327875647844627</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03708883192647326</v>
+        <v>0.0370888319264733</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.02</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="32">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>20800</v>
+        <v>19810</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>18830</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>20550</v>
+        <v>19690</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>22280</v>
+        <v>21868.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>20800</v>
+        <v>19810</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40689,7 +40689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.05</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="32">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19810</v>
+        <v>19470</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>18830</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>19690</v>
+        <v>18270</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>21868.3</v>
+        <v>21525.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9248,11 +9248,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>19810</v>
+        <v>19470</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 22,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,600원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40689,7 +40689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.48</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="32">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19470</v>
+        <v>20000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>21525.7</v>
+        <v>21342.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9248,11 +9248,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>19470</v>
+        <v>20000</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,760원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40689,7 +40689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.28</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="32">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>20000</v>
+        <v>18620</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>18830</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18270</v>
+        <v>17440</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>21342.5</v>
+        <v>20543.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9248,11 +9248,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>20000</v>
+        <v>18620</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,760원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,270원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40689,7 +40689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.59</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="32">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/077970_model.xlsx
+++ b/argus/kship/models/077970_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>22200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18620</v>
+        <v>15780</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>18830</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17440</v>
+        <v>15750</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>24844.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>20543.6</v>
+        <v>19355.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9248,11 +9248,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>18620</v>
+        <v>15780</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,270원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,000원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40689,7 +40689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.79</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="33">
